--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/每日收盤/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{A7D29375-91FD-4C4B-B93D-EE08C49BE211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B833AA7-D1C0-4BED-B06B-CBD4A9B5675E}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{A7D29375-91FD-4C4B-B93D-EE08C49BE211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59BB895F-D656-415A-A0B7-DE1BD84D0A8C}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{1272DF0D-3EAB-4F5B-8D61-874287AAEAA6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
   <si>
     <t>股票名稱</t>
   </si>
@@ -96,6 +96,10 @@
   </si>
   <si>
     <t>印能科技</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上詮</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA9C9C0-9122-4004-885C-7EC096E82716}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.87890625" customWidth="1"/>
@@ -1098,6 +1102,34 @@
         <v>46188</v>
       </c>
     </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="2">
+        <v>100</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2000</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="2">
+        <v>300</v>
+      </c>
+      <c r="C43" s="2">
+        <v>675</v>
+      </c>
+      <c r="D43" s="3">
+        <v>46197</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/每日收盤/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ihsiangtsou-my.sharepoint.com/personal/yihshan_ihsiangtsou_onmicrosoft_com/Documents/GitHub/stock-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{A7D29375-91FD-4C4B-B93D-EE08C49BE211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59BB895F-D656-415A-A0B7-DE1BD84D0A8C}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{A7D29375-91FD-4C4B-B93D-EE08C49BE211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3C40A0B-7F8D-4F6D-BDDE-6BA98BAEC456}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2715" windowWidth="29040" windowHeight="15720" xr2:uid="{1272DF0D-3EAB-4F5B-8D61-874287AAEAA6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t>股票名稱</t>
   </si>
@@ -198,10 +198,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA9C9C0-9122-4004-885C-7EC096E82716}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.87890625" customWidth="1"/>
@@ -1130,6 +1126,20 @@
         <v>46197</v>
       </c>
     </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="2">
+        <v>200</v>
+      </c>
+      <c r="C44" s="2">
+        <v>580</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46199</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -491,7 +491,7 @@
         <v>990</v>
       </c>
       <c r="G2" t="n">
-        <v>675</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>990</v>
       </c>
       <c r="G3" t="n">
-        <v>675</v>
+        <v>637</v>
       </c>
     </row>
     <row r="4">
@@ -616,7 +616,7 @@
         <v>2265</v>
       </c>
       <c r="G7" t="n">
-        <v>818</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         <v>2265</v>
       </c>
       <c r="G8" t="n">
-        <v>818</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="9">
@@ -666,7 +666,7 @@
         <v>2265</v>
       </c>
       <c r="G9" t="n">
-        <v>818</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="10">
@@ -691,7 +691,7 @@
         <v>5310</v>
       </c>
       <c r="G10" t="n">
-        <v>1245</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="11">
@@ -716,7 +716,7 @@
         <v>5310</v>
       </c>
       <c r="G11" t="n">
-        <v>1245</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="12">
@@ -791,7 +791,7 @@
         <v>2520</v>
       </c>
       <c r="G14" t="n">
-        <v>1930</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="15">
@@ -816,7 +816,7 @@
         <v>2520</v>
       </c>
       <c r="G15" t="n">
-        <v>1930</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="16">
@@ -841,7 +841,7 @@
         <v>2855</v>
       </c>
       <c r="G16" t="n">
-        <v>1015</v>
+        <v>1140.75</v>
       </c>
     </row>
     <row r="17">
@@ -866,7 +866,7 @@
         <v>2855</v>
       </c>
       <c r="G17" t="n">
-        <v>1015</v>
+        <v>1140.75</v>
       </c>
     </row>
     <row r="18">
@@ -891,7 +891,7 @@
         <v>2855</v>
       </c>
       <c r="G18" t="n">
-        <v>1015</v>
+        <v>1140.75</v>
       </c>
     </row>
     <row r="19">
@@ -916,7 +916,7 @@
         <v>2855</v>
       </c>
       <c r="G19" t="n">
-        <v>1015</v>
+        <v>1140.75</v>
       </c>
     </row>
     <row r="20">
@@ -941,7 +941,7 @@
         <v>3635</v>
       </c>
       <c r="G20" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="21">
@@ -966,7 +966,7 @@
         <v>3635</v>
       </c>
       <c r="G21" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="22">
@@ -991,7 +991,7 @@
         <v>3635</v>
       </c>
       <c r="G22" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="23">
@@ -1016,7 +1016,7 @@
         <v>3635</v>
       </c>
       <c r="G23" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="24">
@@ -1041,7 +1041,7 @@
         <v>3635</v>
       </c>
       <c r="G24" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="25">
@@ -1066,7 +1066,7 @@
         <v>3635</v>
       </c>
       <c r="G25" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="26">
@@ -1091,7 +1091,7 @@
         <v>3635</v>
       </c>
       <c r="G26" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="27">
@@ -1116,7 +1116,7 @@
         <v>3635</v>
       </c>
       <c r="G27" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="28">
@@ -1141,7 +1141,7 @@
         <v>3635</v>
       </c>
       <c r="G28" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="29">
@@ -1166,7 +1166,7 @@
         <v>3635</v>
       </c>
       <c r="G29" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="30">
@@ -1191,7 +1191,7 @@
         <v>3635</v>
       </c>
       <c r="G30" t="n">
-        <v>1675</v>
+        <v>1704.7</v>
       </c>
     </row>
     <row r="31">
@@ -1241,7 +1241,7 @@
         <v>2715</v>
       </c>
       <c r="G32" t="n">
-        <v>1780</v>
+        <v>1737.5</v>
       </c>
     </row>
     <row r="33">
@@ -1266,7 +1266,7 @@
         <v>2715</v>
       </c>
       <c r="G33" t="n">
-        <v>1780</v>
+        <v>1737.5</v>
       </c>
     </row>
     <row r="34">
@@ -1291,7 +1291,7 @@
         <v>4200</v>
       </c>
       <c r="G34" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="35">
@@ -1316,7 +1316,7 @@
         <v>4200</v>
       </c>
       <c r="G35" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="36">
@@ -1341,7 +1341,7 @@
         <v>4200</v>
       </c>
       <c r="G36" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="37">
@@ -1366,7 +1366,7 @@
         <v>4200</v>
       </c>
       <c r="G37" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="38">
@@ -1391,7 +1391,7 @@
         <v>4200</v>
       </c>
       <c r="G38" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="39">
@@ -1416,7 +1416,7 @@
         <v>4200</v>
       </c>
       <c r="G39" t="n">
-        <v>3345</v>
+        <v>3248.75</v>
       </c>
     </row>
     <row r="40">
@@ -1441,7 +1441,7 @@
         <v>30.81</v>
       </c>
       <c r="G40" t="n">
-        <v>23.38</v>
+        <v>24.4665671641791</v>
       </c>
     </row>
     <row r="41">
@@ -1466,7 +1466,7 @@
         <v>30.81</v>
       </c>
       <c r="G41" t="n">
-        <v>23.38</v>
+        <v>24.4665671641791</v>
       </c>
     </row>
     <row r="42">
@@ -1491,7 +1491,7 @@
         <v>1280</v>
       </c>
       <c r="G42" t="n">
-        <v>968</v>
+        <v>947.1428571428571</v>
       </c>
     </row>
     <row r="43">
@@ -1516,7 +1516,7 @@
         <v>1280</v>
       </c>
       <c r="G43" t="n">
-        <v>968</v>
+        <v>947.1428571428571</v>
       </c>
     </row>
     <row r="44">
@@ -1541,7 +1541,7 @@
         <v>1280</v>
       </c>
       <c r="G44" t="n">
-        <v>968</v>
+        <v>947.1428571428571</v>
       </c>
     </row>
   </sheetData>

--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -1438,7 +1438,7 @@
         <v>15</v>
       </c>
       <c r="F40" t="n">
-        <v>30.81</v>
+        <v>34.57</v>
       </c>
       <c r="G40" t="n">
         <v>24.4665671641791</v>
@@ -1463,7 +1463,7 @@
         <v>15</v>
       </c>
       <c r="F41" t="n">
-        <v>30.81</v>
+        <v>34.57</v>
       </c>
       <c r="G41" t="n">
         <v>24.4665671641791</v>
